--- a/Final_Project/python101_final_project_status.xlsx
+++ b/Final_Project/python101_final_project_status.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Jasthi_P_1st_June_2025\____the_courses_I_teach_organized_Do_Not_Delete\_0__python101_master\____2025_26_Planner\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0021rfv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A18B0427-CE51-4872-A6FD-90E33EB8B877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3135A3-E3D6-4934-99B6-B37D4367D1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB33A5F8-CEA4-49D5-8E58-4BE5F6D5BE59}"/>
   </bookViews>
@@ -36,17 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="38">
   <si>
     <t>Cell 1 (constants)</t>
   </si>
   <si>
-    <t>Cell 2 (process_scores)</t>
-  </si>
-  <si>
-    <t>Cell 3 (parse_emails)</t>
-  </si>
-  <si>
     <t>Cell 4 (student html)</t>
   </si>
   <si>
@@ -92,12 +86,6 @@
     <t>Alternate design</t>
   </si>
   <si>
-    <t>assignments, students</t>
-  </si>
-  <si>
-    <t>email_lookup_table</t>
-  </si>
-  <si>
     <t>WIP</t>
   </si>
   <si>
@@ -123,6 +111,47 @@
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>Aarush</t>
+  </si>
+  <si>
+    <t>Anay</t>
+  </si>
+  <si>
+    <t>Aneesh</t>
+  </si>
+  <si>
+    <t>Meghana</t>
+  </si>
+  <si>
+    <t>Mohnish</t>
+  </si>
+  <si>
+    <t>Nate</t>
+  </si>
+  <si>
+    <t>Rishik</t>
+  </si>
+  <si>
+    <t>Swara</t>
+  </si>
+  <si>
+    <t>Varun</t>
+  </si>
+  <si>
+    <t>Vishwak</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Cell 2 (process_scores)
+assignments, students</t>
+  </si>
+  <si>
+    <t>Cell 3 (parse_emails)
+email_lookup_table</t>
   </si>
 </sst>
 </file>
@@ -146,7 +175,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -165,8 +194,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -189,16 +230,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D4E743D-5FE2-42D1-88BE-A0EC0EB5513A}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -548,323 +607,597 @@
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="4" t="s">
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="B13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="1"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
